--- a/docentes/Castillo Cruz Carlos Samuel - Estadisticos 20231.xlsx
+++ b/docentes/Castillo Cruz Carlos Samuel - Estadisticos 20231.xlsx
@@ -462,10 +462,10 @@
         <v>9</v>
       </c>
       <c r="C2">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -474,7 +474,7 @@
         <v>12</v>
       </c>
       <c r="G2">
-        <v>85.70999999999999</v>
+        <v>100</v>
       </c>
       <c r="H2">
         <v>9.1</v>
@@ -527,10 +527,10 @@
         <v>9</v>
       </c>
       <c r="C2">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D2">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E2">
         <v>12</v>
@@ -589,10 +589,10 @@
         <v>9</v>
       </c>
       <c r="C2">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -601,7 +601,7 @@
         <v>12</v>
       </c>
       <c r="G2">
-        <v>85.70999999999999</v>
+        <v>100</v>
       </c>
       <c r="H2">
         <v>9.1</v>

--- a/docentes/Castillo Cruz Carlos Samuel - Estadisticos 20231.xlsx
+++ b/docentes/Castillo Cruz Carlos Samuel - Estadisticos 20231.xlsx
@@ -530,16 +530,19 @@
         <v>12</v>
       </c>
       <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
         <v>12</v>
       </c>
-      <c r="E2">
-        <v>12</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
       <c r="G2">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H2">
+        <v>9.1</v>
       </c>
     </row>
   </sheetData>
@@ -604,7 +607,7 @@
         <v>100</v>
       </c>
       <c r="H2">
-        <v>9.1</v>
+        <v>9.4</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Castillo Cruz Carlos Samuel - Estadisticos 20231.xlsx
+++ b/docentes/Castillo Cruz Carlos Samuel - Estadisticos 20231.xlsx
@@ -462,7 +462,7 @@
         <v>9</v>
       </c>
       <c r="C2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -471,13 +471,13 @@
         <v>0</v>
       </c>
       <c r="F2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G2">
         <v>100</v>
       </c>
       <c r="H2">
-        <v>9.1</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -527,7 +527,7 @@
         <v>9</v>
       </c>
       <c r="C2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -536,13 +536,13 @@
         <v>0</v>
       </c>
       <c r="F2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G2">
         <v>100</v>
       </c>
       <c r="H2">
-        <v>9.1</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -592,7 +592,7 @@
         <v>9</v>
       </c>
       <c r="C2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -601,13 +601,13 @@
         <v>0</v>
       </c>
       <c r="F2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G2">
         <v>100</v>
       </c>
       <c r="H2">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Castillo Cruz Carlos Samuel - Estadisticos 20231.xlsx
+++ b/docentes/Castillo Cruz Carlos Samuel - Estadisticos 20231.xlsx
@@ -607,7 +607,7 @@
         <v>100</v>
       </c>
       <c r="H2">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Castillo Cruz Carlos Samuel - Estadisticos 20231.xlsx
+++ b/docentes/Castillo Cruz Carlos Samuel - Estadisticos 20231.xlsx
@@ -607,7 +607,7 @@
         <v>100</v>
       </c>
       <c r="H2">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
   </sheetData>
